--- a/crates/pmcp-workbook-compiler/tests/fixtures/leap1900-probe.xlsx
+++ b/crates/pmcp-workbook-compiler/tests/fixtures/leap1900-probe.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Serial" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
+    <definedName name="in_excel_serial">'Serial'!$A$1</definedName>
     <definedName name="out_excel_serial">'Serial'!$B$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
